--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:01</t>
+    <t xml:space="preserve">2026-09-17 13:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:58</t>
+    <t xml:space="preserve">2026-09-23 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:27</t>
+    <t xml:space="preserve">2026-10-02 13:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Penco</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Contulmo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Alto Biobío</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:46</t>
+    <t xml:space="preserve">2026-10-04 08:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:47</t>
+    <t xml:space="preserve">2026-10-05 10:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -733,7 +733,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>749616.62</v>
+        <v>749616.63</v>
       </c>
     </row>
     <row r="12">
@@ -835,7 +835,7 @@
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>681022.62</v>
+        <v>681022.63</v>
       </c>
     </row>
     <row r="18">
@@ -988,7 +988,7 @@
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>618604.12</v>
+        <v>618604.13</v>
       </c>
     </row>
     <row r="27">
@@ -1005,7 +1005,7 @@
         <v>2019</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>614950.12</v>
+        <v>614950.13</v>
       </c>
     </row>
     <row r="28">
@@ -1022,7 +1022,7 @@
         <v>2019</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>614755.12</v>
+        <v>614755.13</v>
       </c>
     </row>
     <row r="29">
@@ -1039,7 +1039,7 @@
         <v>2019</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>610655.62</v>
+        <v>610655.63</v>
       </c>
     </row>
     <row r="30">
@@ -1056,7 +1056,7 @@
         <v>2019</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>600597.12</v>
+        <v>600597.13</v>
       </c>
     </row>
     <row r="31">
